--- a/sample_devices.xlsx
+++ b/sample_devices.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -515,6 +515,21 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>criticality</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>device_type</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>expected_log_types</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -544,6 +559,21 @@
           <t>Primary web server</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>web_server</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>access;error</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -573,6 +603,21 @@
           <t>MySQL production DB</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -602,6 +647,21 @@
           <t>Perimeter firewall</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>firewall</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>traffic;system</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -631,6 +691,21 @@
           <t>Active Directory DC</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>domain_controller</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -660,6 +735,16 @@
           <t>Java app server</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>linux_server</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -689,6 +774,16 @@
           <t>Veeam backup target</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>linux_server</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -718,6 +813,16 @@
           <t>Core L3 switch</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>switch</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -747,6 +852,21 @@
           <t>Snort IDS sensor</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ids</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>alert</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -776,6 +896,16 @@
           <t>Exchange mail gateway</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>email_gateway</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -805,6 +935,21 @@
           <t>Cisco AnyConnect VPN</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>vpn</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>authentication</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -834,6 +979,16 @@
           <t>SAP application server</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>windows_server</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -863,6 +1018,21 @@
           <t>Squid proxy</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -892,6 +1062,16 @@
           <t>Ubuntu 22 workload</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>linux_server</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -921,6 +1101,21 @@
           <t>Windows Server 2022 DC</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>domain_controller</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -948,6 +1143,16 @@
       <c r="G16" s="4" t="inlineStr">
         <is>
           <t>POS log aggregator</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>database</t>
         </is>
       </c>
     </row>
